--- a/РАБОЧИЙ СТОЛ/машины Останкино СЫРЫ.xlsx
+++ b/РАБОЧИЙ СТОЛ/машины Останкино СЫРЫ.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\Заказы на отправку и сортировку\Останкино\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCF7BD10-A859-418F-A0F0-B2580C690083}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39ADA67D-2930-4638-AD6D-7AF14BD40BF3}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>Доброцен-Донецк</t>
   </si>
@@ -85,6 +85,9 @@
   </si>
   <si>
     <t>Малахутин</t>
+  </si>
+  <si>
+    <t>4 машина</t>
   </si>
 </sst>
 </file>
@@ -129,7 +132,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -210,11 +213,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -225,6 +241,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -510,16 +529,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="6" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>9</v>
       </c>
@@ -536,10 +555,13 @@
         <v>13</v>
       </c>
       <c r="F1" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1" s="5" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -547,12 +569,13 @@
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
-      <c r="F2" s="2">
-        <f>B2-C2-D2-E2</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F2" s="2"/>
+      <c r="G2" s="2">
+        <f>B2-C2-D2-E2-F2</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
@@ -560,46 +583,41 @@
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
-      <c r="F3" s="2">
-        <f t="shared" ref="F3:F5" si="0">B3-C3-D3-E3</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F3" s="2"/>
+      <c r="G3" s="2">
+        <f t="shared" ref="G3:G11" si="0">B3-C3-D3-E3-F3</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="2">
-        <v>1565</v>
-      </c>
-      <c r="C4" s="2">
-        <v>1565</v>
-      </c>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
-      <c r="F4" s="2">
+      <c r="F4" s="2"/>
+      <c r="G4" s="2">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="2">
-        <v>2020</v>
-      </c>
-      <c r="C5" s="2">
-        <v>2020</v>
-      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
-      <c r="F5" s="2">
+      <c r="F5" s="2"/>
+      <c r="G5" s="2">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>1</v>
       </c>
@@ -607,12 +625,13 @@
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
-      <c r="F6" s="2">
-        <f t="shared" ref="F6:F11" si="1">B6-C6-D6-E6</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F6" s="2"/>
+      <c r="G6" s="2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>2</v>
       </c>
@@ -620,12 +639,13 @@
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
-      <c r="F7" s="2">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F7" s="2"/>
+      <c r="G7" s="2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>3</v>
       </c>
@@ -633,12 +653,13 @@
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
-      <c r="F8" s="2">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F8" s="2"/>
+      <c r="G8" s="2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>4</v>
       </c>
@@ -646,12 +667,13 @@
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
-      <c r="F9" s="2">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F9" s="2"/>
+      <c r="G9" s="2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>8</v>
       </c>
@@ -659,12 +681,13 @@
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
-      <c r="F10" s="2">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F10" s="2"/>
+      <c r="G10" s="2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>7</v>
       </c>
@@ -672,61 +695,71 @@
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
-      <c r="F11" s="2">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="F11" s="2"/>
+      <c r="G11" s="2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
         <v>16</v>
       </c>
       <c r="B12" s="4">
-        <f>SUM(B2:B11)</f>
-        <v>3585</v>
+        <f t="shared" ref="B12:G12" si="1">SUM(B2:B11)</f>
+        <v>0</v>
       </c>
       <c r="C12" s="4">
-        <f>SUM(C2:C11)</f>
-        <v>3585</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="D12" s="4">
-        <f>SUM(D2:D11)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="E12" s="4">
-        <f>SUM(E2:E11)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="F12" s="4">
-        <f>SUM(F2:F11)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="14" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G12" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="14" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C14" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D14" s="7"/>
       <c r="E14" s="8"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F14" s="9"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C15" s="3">
         <f>IF(ROUNDUP(C12/500,0)&gt;32,32,ROUNDUP(C12/500,0))</f>
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D15" s="3">
-        <f t="shared" ref="D15:E15" si="2">IF(ROUNDUP(D12/500,0)&gt;32,32,ROUNDUP(D12/500,0))</f>
+        <f t="shared" ref="D15:F15" si="2">IF(ROUNDUP(D12/500,0)&gt;32,32,ROUNDUP(D12/500,0))</f>
         <v>0</v>
       </c>
       <c r="E15" s="3">
+        <f t="shared" ref="E15" si="3">IF(ROUNDUP(E12/500,0)&gt;32,32,ROUNDUP(E12/500,0))</f>
+        <v>0</v>
+      </c>
+      <c r="F15" s="3">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="C14:E14"/>
+    <mergeCell ref="C14:F14"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
